--- a/tests/excel_test_file.xlsx
+++ b/tests/excel_test_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mpaulus\repos\mshell\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0062DBA-1630-49C4-96A1-5FB684A22301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834B74C8-0D0F-4D70-92B4-39479AE38519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6550" yWindow="3430" windowWidth="22110" windowHeight="15840" xr2:uid="{7CE5B30E-9ED2-454A-B497-6E473BCD0E9C}"/>
+    <workbookView xWindow="8840" yWindow="3010" windowWidth="22110" windowHeight="15840" xr2:uid="{7CE5B30E-9ED2-454A-B497-6E473BCD0E9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -432,11 +432,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EBBFC0C-CA6E-4ABA-8DD0-BF7E8F85625A}">
-  <dimension ref="A3"/>
+  <dimension ref="C3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
